--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7590A0B3-C1FB-4A74-AC2A-E9A2AEB1A307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5433986D-EEC4-4C16-A83E-89F6644D432C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -523,7 +523,8 @@
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="34" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" customWidth="1"/>
+    <col min="7" max="34" width="9.453125" customWidth="1"/>
     <col min="35" max="35" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -680,8 +681,12 @@
       <c r="C3" s="2">
         <v>70</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="D3" s="1">
+        <v>6439</v>
+      </c>
+      <c r="E3" s="1">
+        <v>75</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -713,11 +718,11 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="2">
         <f>SUM(E3:AH3)</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ3" s="5">
         <f>D3-AI3</f>
-        <v>0</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
@@ -727,8 +732,12 @@
       <c r="C4" s="2">
         <v>70</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="D4" s="1">
+        <v>3274</v>
+      </c>
+      <c r="E4" s="1">
+        <v>40</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -760,11 +769,11 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="2">
         <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>0</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
@@ -774,8 +783,12 @@
       <c r="C5" s="2">
         <v>70</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="D5" s="1">
+        <v>7560</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -811,7 +824,7 @@
       </c>
       <c r="AJ5" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7560</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
@@ -821,8 +834,12 @@
       <c r="C6" s="2">
         <v>120</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="1">
+        <v>13306</v>
+      </c>
+      <c r="E6" s="1">
+        <v>228</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -854,11 +871,11 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13078</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
@@ -868,8 +885,12 @@
       <c r="C7" s="2">
         <v>120</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="1">
+        <v>4623</v>
+      </c>
+      <c r="E7" s="1">
+        <v>257</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -901,11 +922,11 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
@@ -915,8 +936,12 @@
       <c r="C8" s="2">
         <v>120</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="D8" s="1">
+        <v>15904</v>
+      </c>
+      <c r="E8" s="1">
+        <v>187</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -948,11 +973,11 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15717</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
@@ -962,8 +987,12 @@
       <c r="C9" s="2">
         <v>60</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="1">
+        <v>36121</v>
+      </c>
+      <c r="E9" s="1">
+        <v>252</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -995,11 +1024,11 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>35869</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1009,11 +1038,11 @@
       <c r="C10" s="1"/>
       <c r="D10" s="7">
         <f>SUM(D3:D9)</f>
-        <v>0</v>
+        <v>87227</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" ref="E10:AH10" si="2">SUM(E3:E9)</f>
-        <v>0</v>
+        <v>1039</v>
       </c>
       <c r="F10" s="7">
         <f t="shared" si="2"/>
@@ -1133,11 +1162,11 @@
       </c>
       <c r="AI10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1039</v>
       </c>
       <c r="AJ10" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>86188</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1147,11 +1176,11 @@
       <c r="C11" s="1"/>
       <c r="D11" s="7">
         <f>D10/40</f>
-        <v>0</v>
+        <v>2180.6750000000002</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" ref="E11:AH11" si="3">E10/40</f>
-        <v>0</v>
+        <v>25.975000000000001</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="3"/>
@@ -1271,11 +1300,11 @@
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25.975000000000001</v>
       </c>
       <c r="AJ11" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2154.7000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5433986D-EEC4-4C16-A83E-89F6644D432C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7085B69C-87AC-4439-AFF3-064620D7931C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t xml:space="preserve">Total </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Mega Mart </t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUTF Mart </t>
   </si>
 </sst>
 </file>
@@ -111,7 +120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +142,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -203,6 +218,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,6 +692,9 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>6634</v>
+      </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -687,9 +707,13 @@
       <c r="E3" s="1">
         <v>75</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="1">
+        <v>144</v>
+      </c>
+      <c r="H3" s="1">
+        <v>92</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -718,14 +742,17 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="2">
         <f>SUM(E3:AH3)</f>
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="AJ3" s="5">
         <f>D3-AI3</f>
-        <v>6364</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3454</v>
+      </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -738,9 +765,13 @@
       <c r="E4" s="1">
         <v>40</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="1">
+        <v>113</v>
+      </c>
+      <c r="H4" s="1">
+        <v>92</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -769,14 +800,17 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="2">
         <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>3234</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>7800</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,9 +823,13 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -828,6 +866,9 @@
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>13817</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -840,9 +881,13 @@
       <c r="E6" s="1">
         <v>228</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="1">
+        <v>190</v>
+      </c>
+      <c r="H6" s="1">
+        <v>240</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -871,14 +916,17 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="2">
         <f t="shared" si="0"/>
-        <v>228</v>
+        <v>658</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>13078</v>
+        <v>12648</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5115</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,9 +939,13 @@
       <c r="E7" s="1">
         <v>257</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="1">
+        <v>175</v>
+      </c>
+      <c r="H7" s="1">
+        <v>170</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -922,14 +974,17 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="2">
         <f t="shared" si="0"/>
-        <v>257</v>
+        <v>602</v>
       </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>4366</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>16345</v>
+      </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -942,9 +997,13 @@
       <c r="E8" s="1">
         <v>187</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="1">
+        <v>235</v>
+      </c>
+      <c r="H8" s="1">
+        <v>220</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -973,14 +1032,17 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="2">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>642</v>
       </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
-        <v>15717</v>
+        <v>15262</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>36494</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -993,9 +1055,13 @@
       <c r="E9" s="1">
         <v>252</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="1">
+        <v>255</v>
+      </c>
+      <c r="H9" s="1">
+        <v>292</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1024,11 +1090,11 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="2">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>799</v>
       </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
-        <v>35869</v>
+        <v>35322</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1050,11 +1116,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="2"/>
@@ -1162,11 +1228,11 @@
       </c>
       <c r="AI10" s="7">
         <f t="shared" si="0"/>
-        <v>1039</v>
+        <v>3257</v>
       </c>
       <c r="AJ10" s="8">
         <f t="shared" si="1"/>
-        <v>86188</v>
+        <v>83970</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1188,11 +1254,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27.65</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="3"/>
@@ -1300,11 +1366,11 @@
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="0"/>
-        <v>25.975000000000001</v>
+        <v>81.425000000000011</v>
       </c>
       <c r="AJ11" s="8">
         <f t="shared" si="1"/>
-        <v>2154.7000000000003</v>
+        <v>2099.25</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
@@ -1330,16 +1396,32 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="12">
+        <v>46239</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="12">
+        <v>46239</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -1714,7 +1796,7 @@
       <c r="B77" s="1"/>
       <c r="C77" s="5">
         <f>SUM(C14:C76)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D77" s="1"/>
     </row>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7085B69C-87AC-4439-AFF3-064620D7931C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3081670C-7FF4-450B-B79C-8C4DE7FEC35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -97,13 +97,28 @@
   </si>
   <si>
     <t xml:space="preserve">LUTF Mart </t>
+  </si>
+  <si>
+    <t>Aslam Mart LDA</t>
+  </si>
+  <si>
+    <t>Ss Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem </t>
+  </si>
+  <si>
+    <t>Risen Gajumata</t>
+  </si>
+  <si>
+    <t>Zohra Mart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,6 +129,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,13 +211,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -203,14 +223,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -218,8 +249,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,153 +570,161 @@
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" customWidth="1"/>
-    <col min="7" max="34" width="9.453125" customWidth="1"/>
+    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="34" width="9.453125" customWidth="1"/>
     <col min="35" max="35" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="9">
+        <v>46260</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="9"/>
-      <c r="AH1" s="9"/>
-      <c r="AI1" s="9"/>
-      <c r="AJ1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
     </row>
     <row r="2" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>46235</v>
-      </c>
-      <c r="F2" s="3">
-        <v>46236</v>
-      </c>
-      <c r="G2" s="3">
-        <v>46237</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46238</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46239</v>
-      </c>
-      <c r="J2" s="3">
-        <v>46240</v>
-      </c>
-      <c r="K2" s="3">
-        <v>46241</v>
-      </c>
-      <c r="L2" s="3">
-        <v>46242</v>
-      </c>
-      <c r="M2" s="3">
-        <v>46243</v>
-      </c>
-      <c r="N2" s="3">
-        <v>46244</v>
-      </c>
-      <c r="O2" s="3">
-        <v>46245</v>
-      </c>
-      <c r="P2" s="3">
-        <v>46246</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>46247</v>
-      </c>
-      <c r="R2" s="3">
-        <v>46248</v>
-      </c>
-      <c r="S2" s="3">
-        <v>46249</v>
-      </c>
-      <c r="T2" s="3">
-        <v>46250</v>
-      </c>
-      <c r="U2" s="3">
-        <v>46251</v>
-      </c>
-      <c r="V2" s="3">
-        <v>46252</v>
-      </c>
-      <c r="W2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="X2" s="3">
-        <v>46254</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>46255</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>46256</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>46257</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>46258</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>46259</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>46260</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>46261</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>46262</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>46263</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>46264</v>
-      </c>
-      <c r="AI2" s="4" t="s">
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10">
+        <v>2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>3</v>
+      </c>
+      <c r="H2" s="10">
+        <v>4</v>
+      </c>
+      <c r="I2" s="10">
+        <v>5</v>
+      </c>
+      <c r="J2" s="10">
+        <v>6</v>
+      </c>
+      <c r="K2" s="10">
+        <v>7</v>
+      </c>
+      <c r="L2" s="10">
+        <v>8</v>
+      </c>
+      <c r="M2" s="10">
+        <v>9</v>
+      </c>
+      <c r="N2" s="10">
+        <v>10</v>
+      </c>
+      <c r="O2" s="10">
+        <v>11</v>
+      </c>
+      <c r="P2" s="10">
         <v>12</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="Q2" s="10">
+        <v>13</v>
+      </c>
+      <c r="R2" s="10">
+        <v>14</v>
+      </c>
+      <c r="S2" s="10">
+        <v>15</v>
+      </c>
+      <c r="T2" s="10">
+        <v>16</v>
+      </c>
+      <c r="U2" s="10">
+        <v>17</v>
+      </c>
+      <c r="V2" s="10">
+        <v>18</v>
+      </c>
+      <c r="W2" s="10">
+        <v>19</v>
+      </c>
+      <c r="X2" s="10">
+        <v>20</v>
+      </c>
+      <c r="Y2" s="10">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="10">
+        <v>22</v>
+      </c>
+      <c r="AA2" s="10">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="10">
+        <v>24</v>
+      </c>
+      <c r="AC2" s="10">
+        <v>25</v>
+      </c>
+      <c r="AD2" s="10">
+        <v>26</v>
+      </c>
+      <c r="AE2" s="10">
+        <v>27</v>
+      </c>
+      <c r="AF2" s="10">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="10">
+        <v>29</v>
+      </c>
+      <c r="AH2" s="10">
+        <v>30</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -707,14 +744,16 @@
       <c r="E3" s="1">
         <v>75</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="1">
         <v>144</v>
       </c>
       <c r="H3" s="1">
         <v>92</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>260</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -742,11 +781,11 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="2">
         <f>SUM(E3:AH3)</f>
-        <v>311</v>
-      </c>
-      <c r="AJ3" s="5">
+        <v>571</v>
+      </c>
+      <c r="AJ3" s="4">
         <f>D3-AI3</f>
-        <v>6128</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
@@ -765,14 +804,16 @@
       <c r="E4" s="1">
         <v>40</v>
       </c>
-      <c r="F4" s="11"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="1">
         <v>113</v>
       </c>
       <c r="H4" s="1">
         <v>92</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>240</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -800,11 +841,11 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="2">
         <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>245</v>
-      </c>
-      <c r="AJ4" s="5">
+        <v>485</v>
+      </c>
+      <c r="AJ4" s="4">
         <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>3029</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
@@ -823,14 +864,16 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>240</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -858,11 +901,11 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="5">
+        <v>240</v>
+      </c>
+      <c r="AJ5" s="4">
         <f t="shared" si="1"/>
-        <v>7560</v>
+        <v>7320</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
@@ -881,14 +924,16 @@
       <c r="E6" s="1">
         <v>228</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="1">
         <v>190</v>
       </c>
       <c r="H6" s="1">
         <v>240</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>667</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -916,11 +961,11 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="2">
         <f t="shared" si="0"/>
-        <v>658</v>
-      </c>
-      <c r="AJ6" s="5">
+        <v>1325</v>
+      </c>
+      <c r="AJ6" s="4">
         <f t="shared" si="1"/>
-        <v>12648</v>
+        <v>11981</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
@@ -939,14 +984,16 @@
       <c r="E7" s="1">
         <v>257</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="1">
         <v>175</v>
       </c>
       <c r="H7" s="1">
         <v>170</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>730</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -974,11 +1021,11 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="2">
         <f t="shared" si="0"/>
-        <v>602</v>
-      </c>
-      <c r="AJ7" s="5">
+        <v>1332</v>
+      </c>
+      <c r="AJ7" s="4">
         <f t="shared" si="1"/>
-        <v>4021</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
@@ -997,14 +1044,16 @@
       <c r="E8" s="1">
         <v>187</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="1">
         <v>235</v>
       </c>
       <c r="H8" s="1">
         <v>220</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>753</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1032,11 +1081,11 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="2">
         <f t="shared" si="0"/>
-        <v>642</v>
-      </c>
-      <c r="AJ8" s="5">
+        <v>1395</v>
+      </c>
+      <c r="AJ8" s="4">
         <f t="shared" si="1"/>
-        <v>15262</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
@@ -1055,14 +1104,16 @@
       <c r="E9" s="1">
         <v>252</v>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="1">
         <v>255</v>
       </c>
       <c r="H9" s="1">
         <v>292</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>447</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1090,11 +1141,11 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="2">
         <f t="shared" si="0"/>
-        <v>799</v>
-      </c>
-      <c r="AJ9" s="5">
+        <v>1246</v>
+      </c>
+      <c r="AJ9" s="4">
         <f t="shared" si="1"/>
-        <v>35322</v>
+        <v>34875</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1102,137 +1153,137 @@
         <v>10</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <f>SUM(D3:D9)</f>
         <v>87227</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <f t="shared" ref="E10:AH10" si="2">SUM(E3:E9)</f>
         <v>1039</v>
       </c>
-      <c r="F10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="F10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
         <f t="shared" si="2"/>
         <v>1112</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <f t="shared" si="2"/>
         <v>1106</v>
       </c>
-      <c r="I10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AH10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="7">
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
+        <v>3337</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="5">
         <f t="shared" si="0"/>
-        <v>3257</v>
-      </c>
-      <c r="AJ10" s="8">
+        <v>6594</v>
+      </c>
+      <c r="AJ10" s="6">
         <f t="shared" si="1"/>
-        <v>83970</v>
+        <v>80633</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1240,146 +1291,146 @@
         <v>11</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <f>D10/40</f>
         <v>2180.6750000000002</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <f t="shared" ref="E11:AH11" si="3">E10/40</f>
         <v>25.975000000000001</v>
       </c>
-      <c r="F11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="F11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
         <f t="shared" si="3"/>
         <v>27.8</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <f t="shared" si="3"/>
         <v>27.65</v>
       </c>
-      <c r="I11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="7">
+      <c r="I11" s="5">
+        <f t="shared" si="3"/>
+        <v>83.424999999999997</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="5">
         <f t="shared" si="0"/>
-        <v>81.425000000000011</v>
-      </c>
-      <c r="AJ11" s="8">
+        <v>164.85000000000002</v>
+      </c>
+      <c r="AJ11" s="6">
         <f t="shared" si="1"/>
-        <v>2099.25</v>
+        <v>2015.8250000000003</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -1396,7 +1447,7 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+      <c r="A14" s="8">
         <v>46239</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1410,7 +1461,7 @@
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
+      <c r="A15" s="8">
         <v>46239</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1424,34 +1475,74 @@
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="A19" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="1">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
@@ -1794,9 +1885,9 @@
         <v>20</v>
       </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="5">
+      <c r="C77" s="4">
         <f>SUM(C14:C76)</f>
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D77" s="1"/>
     </row>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3081670C-7FF4-450B-B79C-8C4DE7FEC35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB82B3CD-C6DA-4DEC-830D-CCB060D40691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Zohra Mart</t>
+  </si>
+  <si>
+    <t>Sohail Traders</t>
   </si>
 </sst>
 </file>
@@ -754,7 +757,9 @@
       <c r="I3" s="1">
         <v>260</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1">
+        <v>770</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -781,11 +786,11 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="2">
         <f>SUM(E3:AH3)</f>
-        <v>571</v>
+        <v>1341</v>
       </c>
       <c r="AJ3" s="4">
         <f>D3-AI3</f>
-        <v>5868</v>
+        <v>5098</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
@@ -814,7 +819,9 @@
       <c r="I4" s="1">
         <v>240</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1">
+        <v>582</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -841,11 +848,11 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="2">
         <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>485</v>
+        <v>1067</v>
       </c>
       <c r="AJ4" s="4">
         <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>2789</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
@@ -874,7 +881,9 @@
       <c r="I5" s="1">
         <v>240</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1">
+        <v>679</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -901,11 +910,11 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="2">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>919</v>
       </c>
       <c r="AJ5" s="4">
         <f t="shared" si="1"/>
-        <v>7320</v>
+        <v>6641</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
@@ -934,7 +943,9 @@
       <c r="I6" s="1">
         <v>667</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <v>1577</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -961,11 +972,11 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="2">
         <f t="shared" si="0"/>
-        <v>1325</v>
+        <v>2902</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="1"/>
-        <v>11981</v>
+        <v>10404</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
@@ -994,7 +1005,9 @@
       <c r="I7" s="1">
         <v>730</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1">
+        <v>1572</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1021,11 +1034,11 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="2">
         <f t="shared" si="0"/>
-        <v>1332</v>
+        <v>2904</v>
       </c>
       <c r="AJ7" s="4">
         <f t="shared" si="1"/>
-        <v>3291</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
@@ -1054,7 +1067,9 @@
       <c r="I8" s="1">
         <v>753</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1">
+        <v>2315</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1081,11 +1096,11 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="2">
         <f t="shared" si="0"/>
-        <v>1395</v>
+        <v>3710</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="1"/>
-        <v>14509</v>
+        <v>12194</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
@@ -1114,7 +1129,9 @@
       <c r="I9" s="1">
         <v>447</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <v>2234</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1141,11 +1158,11 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="2">
         <f t="shared" si="0"/>
-        <v>1246</v>
+        <v>3480</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" si="1"/>
-        <v>34875</v>
+        <v>32641</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1179,7 +1196,7 @@
       </c>
       <c r="J10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9729</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="2"/>
@@ -1279,11 +1296,11 @@
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="0"/>
-        <v>6594</v>
+        <v>16323</v>
       </c>
       <c r="AJ10" s="6">
         <f t="shared" si="1"/>
-        <v>80633</v>
+        <v>70904</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1317,7 +1334,7 @@
       </c>
       <c r="J11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>243.22499999999999</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="3"/>
@@ -1417,11 +1434,11 @@
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="0"/>
-        <v>164.85000000000002</v>
+        <v>408.07500000000005</v>
       </c>
       <c r="AJ11" s="6">
         <f t="shared" si="1"/>
-        <v>2015.8250000000003</v>
+        <v>1772.6000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
@@ -1545,10 +1562,18 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="A21" s="8">
+        <v>46240</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
@@ -1887,7 +1912,7 @@
       <c r="B77" s="1"/>
       <c r="C77" s="4">
         <f>SUM(C14:C76)</f>
-        <v>143</v>
+        <v>243</v>
       </c>
       <c r="D77" s="1"/>
     </row>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB82B3CD-C6DA-4DEC-830D-CCB060D40691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D12DC1-3EDD-49C8-87B1-A542ABF58C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -115,6 +115,30 @@
   </si>
   <si>
     <t>Sohail Traders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Foods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Behria Town </t>
+  </si>
+  <si>
+    <t>Imperia Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Shadra </t>
+  </si>
+  <si>
+    <t>Rainbow Shikhupura</t>
+  </si>
+  <si>
+    <t>Rainbow Gujranwala</t>
+  </si>
+  <si>
+    <t>Zubaida Associates</t>
   </si>
 </sst>
 </file>
@@ -566,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AJ77"/>
+  <dimension ref="A1:AJ76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -578,7 +602,9 @@
     <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="34" width="9.453125" customWidth="1"/>
+    <col min="10" max="12" width="9.453125" customWidth="1"/>
+    <col min="13" max="33" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="9.453125" customWidth="1"/>
     <col min="35" max="35" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -732,9 +758,6 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>6634</v>
-      </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -760,8 +783,12 @@
       <c r="J3" s="1">
         <v>770</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="K3" s="1">
+        <v>319</v>
+      </c>
+      <c r="L3" s="1">
+        <v>897</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -786,17 +813,14 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="2">
         <f>SUM(E3:AH3)</f>
-        <v>1341</v>
+        <v>2557</v>
       </c>
       <c r="AJ3" s="4">
         <f>D3-AI3</f>
-        <v>5098</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3454</v>
-      </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -822,8 +846,12 @@
       <c r="J4" s="1">
         <v>582</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1">
+        <v>481</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1025</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -848,17 +876,14 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="2">
         <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>1067</v>
+        <v>2573</v>
       </c>
       <c r="AJ4" s="4">
         <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>2207</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>7800</v>
-      </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,8 +909,12 @@
       <c r="J5" s="1">
         <v>679</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1">
+        <v>179</v>
+      </c>
+      <c r="L5" s="1">
+        <v>3471</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -910,17 +939,14 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="2">
         <f t="shared" si="0"/>
-        <v>919</v>
+        <v>4569</v>
       </c>
       <c r="AJ5" s="4">
         <f t="shared" si="1"/>
-        <v>6641</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>13817</v>
-      </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +972,12 @@
       <c r="J6" s="1">
         <v>1577</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1">
+        <v>559</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1223</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -972,17 +1002,14 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="2">
         <f t="shared" si="0"/>
-        <v>2902</v>
+        <v>4684</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="1"/>
-        <v>10404</v>
+        <v>8622</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5115</v>
-      </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1008,8 +1035,12 @@
       <c r="J7" s="1">
         <v>1572</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1">
+        <v>418</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1496</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1034,17 +1065,14 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="2">
         <f t="shared" si="0"/>
-        <v>2904</v>
+        <v>4818</v>
       </c>
       <c r="AJ7" s="4">
         <f t="shared" si="1"/>
-        <v>1719</v>
+        <v>-195</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>16345</v>
-      </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1070,8 +1098,12 @@
       <c r="J8" s="1">
         <v>2315</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1">
+        <v>966</v>
+      </c>
+      <c r="L8" s="1">
+        <v>2745</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1096,17 +1128,14 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="2">
         <f t="shared" si="0"/>
-        <v>3710</v>
+        <v>7421</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="1"/>
-        <v>12194</v>
+        <v>8483</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>36494</v>
-      </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1132,8 +1161,12 @@
       <c r="J9" s="1">
         <v>2234</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1">
+        <v>263</v>
+      </c>
+      <c r="L9" s="1">
+        <v>136</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1158,11 +1191,11 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="2">
         <f t="shared" si="0"/>
-        <v>3480</v>
+        <v>3879</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" si="1"/>
-        <v>32641</v>
+        <v>32242</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1200,11 +1233,11 @@
       </c>
       <c r="K10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3185</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10993</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" si="2"/>
@@ -1296,11 +1329,11 @@
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="0"/>
-        <v>16323</v>
+        <v>30501</v>
       </c>
       <c r="AJ10" s="6">
         <f t="shared" si="1"/>
-        <v>70904</v>
+        <v>56726</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1338,11 +1371,11 @@
       </c>
       <c r="K11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>79.625</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.82499999999999</v>
       </c>
       <c r="M11" s="5">
         <f t="shared" si="3"/>
@@ -1434,11 +1467,11 @@
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="0"/>
-        <v>408.07500000000005</v>
+        <v>762.52500000000009</v>
       </c>
       <c r="AJ11" s="6">
         <f t="shared" si="1"/>
-        <v>1772.6000000000001</v>
+        <v>1418.15</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
@@ -1576,52 +1609,116 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="A22" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
+        <v>35</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="A23" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="A24" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="A25" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="1">
+        <v>6.55</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="1">
+        <v>21.975000000000001</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="A27" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="1">
+        <v>13</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="A28" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1">
+        <v>15</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="A29" s="8">
+        <v>46242</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="1">
+        <v>190</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
@@ -1900,21 +1997,15 @@
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="1"/>
+      <c r="A76" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
+      <c r="C76" s="4">
+        <f>SUM(C14:C75)</f>
+        <v>562.32500000000005</v>
+      </c>
       <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="4">
-        <f>SUM(C14:C76)</f>
-        <v>243</v>
-      </c>
-      <c r="D77" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D12DC1-3EDD-49C8-87B1-A542ABF58C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEB0593-8ABC-4E12-AC78-2B6200428AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -139,6 +139,27 @@
   </si>
   <si>
     <t>Zubaida Associates</t>
+  </si>
+  <si>
+    <t>Green Velly</t>
+  </si>
+  <si>
+    <t>Rainbow Defence Road</t>
+  </si>
+  <si>
+    <t>Rainbow EME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Wapda Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Model Town </t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Behria Town </t>
   </si>
 </sst>
 </file>
@@ -238,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -268,6 +289,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -590,67 +620,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AJ76"/>
+  <dimension ref="A1:AL76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" customWidth="1"/>
-    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="9.453125" customWidth="1"/>
-    <col min="13" max="33" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="9.453125" customWidth="1"/>
-    <col min="35" max="35" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="9.453125" customWidth="1"/>
+    <col min="15" max="15" width="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.453125" customWidth="1"/>
+    <col min="18" max="35" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="6.08984375" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9">
         <v>46260</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-    </row>
-    <row r="2" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+    </row>
+    <row r="2" spans="1:38" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -660,104 +694,110 @@
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="15">
+        <v>46243</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="10">
         <v>1</v>
       </c>
-      <c r="F2" s="10">
+      <c r="H2" s="10">
         <v>2</v>
       </c>
-      <c r="G2" s="10">
+      <c r="I2" s="10">
         <v>3</v>
       </c>
-      <c r="H2" s="10">
+      <c r="J2" s="10">
         <v>4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="K2" s="10">
         <v>5</v>
       </c>
-      <c r="J2" s="10">
+      <c r="L2" s="10">
         <v>6</v>
       </c>
-      <c r="K2" s="10">
+      <c r="M2" s="10">
         <v>7</v>
       </c>
-      <c r="L2" s="10">
+      <c r="N2" s="10">
         <v>8</v>
       </c>
-      <c r="M2" s="10">
+      <c r="O2" s="10">
         <v>9</v>
       </c>
-      <c r="N2" s="10">
+      <c r="P2" s="10">
         <v>10</v>
       </c>
-      <c r="O2" s="10">
+      <c r="Q2" s="10">
         <v>11</v>
       </c>
-      <c r="P2" s="10">
+      <c r="R2" s="10">
         <v>12</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="S2" s="10">
         <v>13</v>
       </c>
-      <c r="R2" s="10">
+      <c r="T2" s="10">
         <v>14</v>
       </c>
-      <c r="S2" s="10">
+      <c r="U2" s="10">
         <v>15</v>
       </c>
-      <c r="T2" s="10">
+      <c r="V2" s="10">
         <v>16</v>
       </c>
-      <c r="U2" s="10">
+      <c r="W2" s="10">
         <v>17</v>
       </c>
-      <c r="V2" s="10">
+      <c r="X2" s="10">
         <v>18</v>
       </c>
-      <c r="W2" s="10">
+      <c r="Y2" s="10">
         <v>19</v>
       </c>
-      <c r="X2" s="10">
+      <c r="Z2" s="10">
         <v>20</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="AA2" s="10">
         <v>21</v>
       </c>
-      <c r="Z2" s="10">
-        <v>22</v>
-      </c>
-      <c r="AA2" s="10">
+      <c r="AB2" s="10">
+        <v>22</v>
+      </c>
+      <c r="AC2" s="10">
         <v>23</v>
       </c>
-      <c r="AB2" s="10">
+      <c r="AD2" s="10">
         <v>24</v>
       </c>
-      <c r="AC2" s="10">
+      <c r="AE2" s="10">
         <v>25</v>
       </c>
-      <c r="AD2" s="10">
+      <c r="AF2" s="10">
         <v>26</v>
       </c>
-      <c r="AE2" s="10">
+      <c r="AG2" s="10">
         <v>27</v>
       </c>
-      <c r="AF2" s="10">
+      <c r="AH2" s="10">
         <v>28</v>
       </c>
-      <c r="AG2" s="10">
+      <c r="AI2" s="10">
         <v>29</v>
       </c>
-      <c r="AH2" s="10">
+      <c r="AJ2" s="10">
         <v>30</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AK2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AL2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,35 +805,44 @@
         <v>70</v>
       </c>
       <c r="D3" s="1">
-        <v>6439</v>
+        <v>6769</v>
       </c>
       <c r="E3" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F3" s="1">
+        <f>E3+D3</f>
+        <v>14769</v>
+      </c>
+      <c r="G3" s="1">
         <v>75</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="1">
+      <c r="H3" s="7"/>
+      <c r="I3" s="1">
         <v>144</v>
       </c>
-      <c r="H3" s="1">
+      <c r="J3" s="1">
         <v>92</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>260</v>
       </c>
-      <c r="J3" s="1">
+      <c r="L3" s="1">
         <v>770</v>
       </c>
-      <c r="K3" s="1">
-        <v>319</v>
-      </c>
-      <c r="L3" s="1">
-        <v>897</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="M3" s="1">
+        <v>279</v>
+      </c>
+      <c r="N3" s="1">
+        <v>939</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="1">
+        <v>642</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>300</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -811,16 +860,18 @@
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
-      <c r="AI3" s="2">
-        <f>SUM(E3:AH3)</f>
-        <v>2557</v>
-      </c>
-      <c r="AJ3" s="4">
-        <f>D3-AI3</f>
-        <v>3882</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="2">
+        <f>SUM(G3:AJ3)</f>
+        <v>3501</v>
+      </c>
+      <c r="AL3" s="4">
+        <f>F3-AK3</f>
+        <v>11268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -828,35 +879,44 @@
         <v>70</v>
       </c>
       <c r="D4" s="1">
-        <v>3274</v>
+        <v>3137</v>
       </c>
       <c r="E4" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F9" si="0">E4+D4</f>
+        <v>11137</v>
+      </c>
+      <c r="G4" s="1">
         <v>40</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="1">
+      <c r="H4" s="7"/>
+      <c r="I4" s="1">
         <v>113</v>
       </c>
-      <c r="H4" s="1">
+      <c r="J4" s="1">
         <v>92</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>240</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>582</v>
       </c>
-      <c r="K4" s="1">
+      <c r="M4" s="1">
         <v>481</v>
       </c>
-      <c r="L4" s="1">
-        <v>1025</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
+      <c r="N4" s="1">
+        <v>1041</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="1">
+        <v>812</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>337</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -874,16 +934,18 @@
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
-      <c r="AI4" s="2">
-        <f t="shared" ref="AI4:AI11" si="0">SUM(E4:AH4)</f>
-        <v>2573</v>
-      </c>
-      <c r="AJ4" s="4">
-        <f t="shared" ref="AJ4:AJ11" si="1">D4-AI4</f>
-        <v>701</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="2">
+        <f t="shared" ref="AK4:AK11" si="1">SUM(G4:AJ4)</f>
+        <v>3738</v>
+      </c>
+      <c r="AL4" s="4">
+        <f t="shared" ref="AL4:AL9" si="2">F4-AK4</f>
+        <v>7399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,35 +953,44 @@
         <v>70</v>
       </c>
       <c r="D5" s="1">
-        <v>7560</v>
+        <v>7361</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>8000</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>15361</v>
+      </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
+      <c r="H5" s="7"/>
       <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>240</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L5" s="1">
         <v>679</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>179</v>
       </c>
-      <c r="L5" s="1">
-        <v>3471</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="N5" s="1">
+        <v>3557</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="1">
+        <v>770</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>215</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -937,16 +1008,18 @@
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
-      <c r="AI5" s="2">
-        <f t="shared" si="0"/>
-        <v>4569</v>
-      </c>
-      <c r="AJ5" s="4">
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="2">
         <f t="shared" si="1"/>
-        <v>2991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+        <v>5640</v>
+      </c>
+      <c r="AL5" s="4">
+        <f t="shared" si="2"/>
+        <v>9721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -954,35 +1027,42 @@
         <v>120</v>
       </c>
       <c r="D6" s="1">
-        <v>13306</v>
-      </c>
-      <c r="E6" s="1">
+        <v>13138</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>13138</v>
+      </c>
+      <c r="G6" s="1">
         <v>228</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="1">
+      <c r="H6" s="7"/>
+      <c r="I6" s="1">
         <v>190</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>240</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>667</v>
       </c>
-      <c r="J6" s="1">
+      <c r="L6" s="1">
         <v>1577</v>
       </c>
-      <c r="K6" s="1">
-        <v>559</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1223</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
+      <c r="M6" s="1">
+        <v>539</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1264</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="1">
+        <v>947</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>574</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1000,16 +1080,18 @@
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
-      <c r="AI6" s="2">
-        <f t="shared" si="0"/>
-        <v>4684</v>
-      </c>
-      <c r="AJ6" s="4">
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="2">
         <f t="shared" si="1"/>
-        <v>8622</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+        <v>6226</v>
+      </c>
+      <c r="AL6" s="4">
+        <f t="shared" si="2"/>
+        <v>6912</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1017,35 +1099,44 @@
         <v>120</v>
       </c>
       <c r="D7" s="1">
-        <v>4623</v>
+        <v>4387</v>
       </c>
       <c r="E7" s="1">
+        <v>12000</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>16387</v>
+      </c>
+      <c r="G7" s="1">
         <v>257</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="1">
+      <c r="H7" s="7"/>
+      <c r="I7" s="1">
         <v>175</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>170</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>730</v>
       </c>
-      <c r="J7" s="1">
+      <c r="L7" s="1">
         <v>1572</v>
       </c>
-      <c r="K7" s="1">
-        <v>418</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1496</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="M7" s="1">
+        <v>398</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1562</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="1">
+        <v>1059</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>389</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1063,16 +1154,18 @@
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
-      <c r="AI7" s="2">
-        <f t="shared" si="0"/>
-        <v>4818</v>
-      </c>
-      <c r="AJ7" s="4">
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="2">
         <f t="shared" si="1"/>
-        <v>-195</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+        <v>6312</v>
+      </c>
+      <c r="AL7" s="4">
+        <f t="shared" si="2"/>
+        <v>10075</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1080,35 +1173,42 @@
         <v>120</v>
       </c>
       <c r="D8" s="1">
-        <v>15904</v>
-      </c>
-      <c r="E8" s="1">
+        <v>15754</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>15754</v>
+      </c>
+      <c r="G8" s="1">
         <v>187</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="1">
+      <c r="H8" s="7"/>
+      <c r="I8" s="1">
         <v>235</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>220</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>753</v>
       </c>
-      <c r="J8" s="1">
+      <c r="L8" s="1">
         <v>2315</v>
       </c>
-      <c r="K8" s="1">
-        <v>966</v>
-      </c>
-      <c r="L8" s="1">
-        <v>2745</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
+      <c r="M8" s="1">
+        <v>946</v>
+      </c>
+      <c r="N8" s="1">
+        <v>2794</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="1">
+        <v>1402</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>602</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1126,16 +1226,18 @@
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
-      <c r="AI8" s="2">
-        <f t="shared" si="0"/>
-        <v>7421</v>
-      </c>
-      <c r="AJ8" s="4">
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="2">
         <f t="shared" si="1"/>
-        <v>8483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+        <v>9454</v>
+      </c>
+      <c r="AL8" s="4">
+        <f t="shared" si="2"/>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,35 +1245,42 @@
         <v>60</v>
       </c>
       <c r="D9" s="1">
-        <v>36121</v>
-      </c>
-      <c r="E9" s="1">
+        <v>34015</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>34015</v>
+      </c>
+      <c r="G9" s="1">
         <v>252</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="1">
+      <c r="H9" s="7"/>
+      <c r="I9" s="1">
         <v>255</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>292</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>447</v>
       </c>
-      <c r="J9" s="1">
+      <c r="L9" s="1">
         <v>2234</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>263</v>
       </c>
-      <c r="L9" s="1">
-        <v>136</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
+      <c r="N9" s="1">
+        <v>148</v>
+      </c>
+      <c r="O9" s="7"/>
+      <c r="P9" s="1">
+        <v>652</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>472</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1189,300 +1298,320 @@
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
-      <c r="AI9" s="2">
-        <f t="shared" si="0"/>
-        <v>3879</v>
-      </c>
-      <c r="AJ9" s="4">
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="2">
         <f t="shared" si="1"/>
-        <v>32242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>5015</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="2"/>
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
         <f>SUM(D3:D9)</f>
-        <v>87227</v>
+        <v>84561</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" ref="E10:AH10" si="2">SUM(E3:E9)</f>
+        <f>SUM(E3:E9)</f>
+        <v>36000</v>
+      </c>
+      <c r="F10" s="5">
+        <f>SUM(F3:F9)</f>
+        <v>120561</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" ref="G10:AJ10" si="3">SUM(G3:G9)</f>
         <v>1039</v>
       </c>
-      <c r="F10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <f t="shared" si="2"/>
+      <c r="H10" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="3"/>
         <v>1112</v>
       </c>
-      <c r="H10" s="5">
-        <f t="shared" si="2"/>
+      <c r="J10" s="5">
+        <f t="shared" si="3"/>
         <v>1106</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" si="2"/>
+      <c r="K10" s="5">
+        <f t="shared" si="3"/>
         <v>3337</v>
       </c>
-      <c r="J10" s="5">
-        <f t="shared" si="2"/>
+      <c r="L10" s="5">
+        <f t="shared" si="3"/>
         <v>9729</v>
       </c>
-      <c r="K10" s="5">
-        <f t="shared" si="2"/>
-        <v>3185</v>
-      </c>
-      <c r="L10" s="5">
-        <f t="shared" si="2"/>
-        <v>10993</v>
-      </c>
       <c r="M10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>3085</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>11305</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>6284</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>2889</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="0"/>
-        <v>30501</v>
-      </c>
-      <c r="AJ10" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK10" s="5">
         <f t="shared" si="1"/>
-        <v>56726</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <v>39886</v>
+      </c>
+      <c r="AL10" s="6">
+        <f t="shared" ref="AL10:AL11" si="4">D10-AK10</f>
+        <v>44675</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
         <f>D10/40</f>
-        <v>2180.6750000000002</v>
+        <v>2114.0250000000001</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" ref="E11:AH11" si="3">E10/40</f>
+        <f>E10/40</f>
+        <v>900</v>
+      </c>
+      <c r="F11" s="5">
+        <f>F10/40</f>
+        <v>3014.0250000000001</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ref="G11:AJ11" si="5">G10/40</f>
         <v>25.975000000000001</v>
       </c>
-      <c r="F11" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" si="3"/>
+      <c r="H11" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="5"/>
         <v>27.8</v>
       </c>
-      <c r="H11" s="5">
-        <f t="shared" si="3"/>
+      <c r="J11" s="5">
+        <f t="shared" si="5"/>
         <v>27.65</v>
       </c>
-      <c r="I11" s="5">
-        <f t="shared" si="3"/>
+      <c r="K11" s="5">
+        <f t="shared" si="5"/>
         <v>83.424999999999997</v>
       </c>
-      <c r="J11" s="5">
-        <f t="shared" si="3"/>
+      <c r="L11" s="5">
+        <f t="shared" si="5"/>
         <v>243.22499999999999</v>
       </c>
-      <c r="K11" s="5">
-        <f t="shared" si="3"/>
-        <v>79.625</v>
-      </c>
-      <c r="L11" s="5">
-        <f t="shared" si="3"/>
-        <v>274.82499999999999</v>
-      </c>
       <c r="M11" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>77.125</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>282.625</v>
       </c>
       <c r="O11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P11" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>157.1</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>72.224999999999994</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="0"/>
-        <v>762.52500000000009</v>
-      </c>
-      <c r="AJ11" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="5">
         <f t="shared" si="1"/>
-        <v>1418.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+        <v>997.15000000000009</v>
+      </c>
+      <c r="AL11" s="6">
+        <f t="shared" si="4"/>
+        <v>1116.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1495,8 +1624,10 @@
       <c r="D13" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>46239</v>
       </c>
@@ -1510,7 +1641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>46239</v>
       </c>
@@ -1524,7 +1655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>46240</v>
       </c>
@@ -1721,46 +1852,102 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="1">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="A31" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="1">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="A32" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="A33" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="1">
+        <v>17</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="A34" s="8">
+        <v>46244</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="1">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="A35" s="8">
+        <v>46245</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="1">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="A36" s="8">
+        <v>46245</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="1">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
@@ -2003,13 +2190,13 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>562.32500000000005</v>
+        <v>661.32500000000005</v>
       </c>
       <c r="D76" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:AJ1"/>
+    <mergeCell ref="B1:AL1"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEB0593-8ABC-4E12-AC78-2B6200428AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED8421F-95CC-468F-93D1-512919BBE6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -160,6 +160,21 @@
   </si>
   <si>
     <t xml:space="preserve">Rainbow Behria Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Rachna Block </t>
+  </si>
+  <si>
+    <t>HKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Gajumata </t>
+  </si>
+  <si>
+    <t>Nabeel Traders</t>
   </si>
 </sst>
 </file>
@@ -634,8 +649,8 @@
     <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="9.453125" customWidth="1"/>
     <col min="15" max="15" width="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="9.453125" customWidth="1"/>
-    <col min="18" max="35" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="16" max="18" width="9.453125" customWidth="1"/>
+    <col min="19" max="35" width="9.453125" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="6.08984375" hidden="1" customWidth="1"/>
     <col min="37" max="37" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -843,7 +858,9 @@
       <c r="Q3" s="1">
         <v>300</v>
       </c>
-      <c r="R3" s="1"/>
+      <c r="R3" s="1">
+        <v>2268</v>
+      </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -864,11 +881,11 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="2">
         <f>SUM(G3:AJ3)</f>
-        <v>3501</v>
+        <v>5769</v>
       </c>
       <c r="AL3" s="4">
         <f>F3-AK3</f>
-        <v>11268</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.35">
@@ -917,7 +934,9 @@
       <c r="Q4" s="1">
         <v>337</v>
       </c>
-      <c r="R4" s="1"/>
+      <c r="R4" s="1">
+        <v>2028</v>
+      </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -938,11 +957,11 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="2">
         <f t="shared" ref="AK4:AK11" si="1">SUM(G4:AJ4)</f>
-        <v>3738</v>
+        <v>5766</v>
       </c>
       <c r="AL4" s="4">
         <f t="shared" ref="AL4:AL9" si="2">F4-AK4</f>
-        <v>7399</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.35">
@@ -991,7 +1010,9 @@
       <c r="Q5" s="1">
         <v>215</v>
       </c>
-      <c r="R5" s="1"/>
+      <c r="R5" s="1">
+        <v>1290</v>
+      </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
@@ -1012,11 +1033,11 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="2">
         <f t="shared" si="1"/>
-        <v>5640</v>
+        <v>6930</v>
       </c>
       <c r="AL5" s="4">
         <f t="shared" si="2"/>
-        <v>9721</v>
+        <v>8431</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.35">
@@ -1063,7 +1084,9 @@
       <c r="Q6" s="1">
         <v>574</v>
       </c>
-      <c r="R6" s="1"/>
+      <c r="R6" s="1">
+        <v>4766</v>
+      </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
@@ -1084,11 +1107,11 @@
       <c r="AJ6" s="1"/>
       <c r="AK6" s="2">
         <f t="shared" si="1"/>
-        <v>6226</v>
+        <v>10992</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="2"/>
-        <v>6912</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.35">
@@ -1137,7 +1160,9 @@
       <c r="Q7" s="1">
         <v>389</v>
       </c>
-      <c r="R7" s="1"/>
+      <c r="R7" s="1">
+        <v>3744</v>
+      </c>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1158,11 +1183,11 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2">
         <f t="shared" si="1"/>
-        <v>6312</v>
+        <v>10056</v>
       </c>
       <c r="AL7" s="4">
         <f t="shared" si="2"/>
-        <v>10075</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.35">
@@ -1209,7 +1234,9 @@
       <c r="Q8" s="1">
         <v>602</v>
       </c>
-      <c r="R8" s="1"/>
+      <c r="R8" s="1">
+        <v>3669</v>
+      </c>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -1230,11 +1257,11 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2">
         <f t="shared" si="1"/>
-        <v>9454</v>
+        <v>13123</v>
       </c>
       <c r="AL8" s="4">
         <f t="shared" si="2"/>
-        <v>6300</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.35">
@@ -1281,7 +1308,9 @@
       <c r="Q9" s="1">
         <v>472</v>
       </c>
-      <c r="R9" s="1"/>
+      <c r="R9" s="1">
+        <v>4366</v>
+      </c>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -1302,11 +1331,11 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2">
         <f t="shared" si="1"/>
-        <v>5015</v>
+        <v>9381</v>
       </c>
       <c r="AL9" s="4">
         <f t="shared" si="2"/>
-        <v>29000</v>
+        <v>24634</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1372,7 +1401,7 @@
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>22131</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
@@ -1448,11 +1477,11 @@
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="1"/>
-        <v>39886</v>
+        <v>62017</v>
       </c>
       <c r="AL10" s="6">
         <f t="shared" ref="AL10:AL11" si="4">D10-AK10</f>
-        <v>44675</v>
+        <v>22544</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1518,7 +1547,7 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>553.27499999999998</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="5"/>
@@ -1594,11 +1623,11 @@
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="1"/>
-        <v>997.15000000000009</v>
+        <v>1550.4250000000002</v>
       </c>
       <c r="AL11" s="6">
         <f t="shared" si="4"/>
-        <v>1116.875</v>
+        <v>563.59999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.35">
@@ -1950,40 +1979,88 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="A37" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="A38" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="1">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="A39" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="A40" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="1">
+        <v>16</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="A41" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1">
+        <v>17</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+      <c r="A42" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="1">
+        <v>450</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
@@ -2190,7 +2267,7 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>661.32500000000005</v>
+        <v>1185.825</v>
       </c>
       <c r="D76" s="1"/>
     </row>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED8421F-95CC-468F-93D1-512919BBE6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7774586D-D048-48BF-A528-2466C8055DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>Nabeel Traders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goutmet MIX </t>
+  </si>
+  <si>
+    <t>Rainbow Barki Road</t>
+  </si>
+  <si>
+    <t>Euro Fateh Ghar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons </t>
   </si>
 </sst>
 </file>
@@ -274,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -321,6 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,8 +662,8 @@
     <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="9.453125" customWidth="1"/>
     <col min="15" max="15" width="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="9.453125" customWidth="1"/>
-    <col min="19" max="35" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="16" max="19" width="9.453125" customWidth="1"/>
+    <col min="20" max="35" width="9.453125" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="6.08984375" hidden="1" customWidth="1"/>
     <col min="37" max="37" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -861,7 +874,9 @@
       <c r="R3" s="1">
         <v>2268</v>
       </c>
-      <c r="S3" s="1"/>
+      <c r="S3" s="1">
+        <v>184</v>
+      </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -881,11 +896,11 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="2">
         <f>SUM(G3:AJ3)</f>
-        <v>5769</v>
+        <v>5953</v>
       </c>
       <c r="AL3" s="4">
         <f>F3-AK3</f>
-        <v>9000</v>
+        <v>8816</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.35">
@@ -937,7 +952,9 @@
       <c r="R4" s="1">
         <v>2028</v>
       </c>
-      <c r="S4" s="1"/>
+      <c r="S4" s="1">
+        <v>158</v>
+      </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -957,11 +974,11 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="2">
         <f t="shared" ref="AK4:AK11" si="1">SUM(G4:AJ4)</f>
-        <v>5766</v>
+        <v>5924</v>
       </c>
       <c r="AL4" s="4">
         <f t="shared" ref="AL4:AL9" si="2">F4-AK4</f>
-        <v>5371</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.35">
@@ -1013,7 +1030,9 @@
       <c r="R5" s="1">
         <v>1290</v>
       </c>
-      <c r="S5" s="1"/>
+      <c r="S5" s="1">
+        <v>339</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1033,11 +1052,11 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="2">
         <f t="shared" si="1"/>
-        <v>6930</v>
+        <v>7269</v>
       </c>
       <c r="AL5" s="4">
         <f t="shared" si="2"/>
-        <v>8431</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.35">
@@ -1085,9 +1104,11 @@
         <v>574</v>
       </c>
       <c r="R6" s="1">
-        <v>4766</v>
-      </c>
-      <c r="S6" s="1"/>
+        <v>5646</v>
+      </c>
+      <c r="S6" s="1">
+        <v>367</v>
+      </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1107,11 +1128,11 @@
       <c r="AJ6" s="1"/>
       <c r="AK6" s="2">
         <f t="shared" si="1"/>
-        <v>10992</v>
+        <v>12239</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="2"/>
-        <v>2146</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.35">
@@ -1161,9 +1182,11 @@
         <v>389</v>
       </c>
       <c r="R7" s="1">
-        <v>3744</v>
-      </c>
-      <c r="S7" s="1"/>
+        <v>4384</v>
+      </c>
+      <c r="S7" s="1">
+        <v>255</v>
+      </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1183,11 +1206,11 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2">
         <f t="shared" si="1"/>
-        <v>10056</v>
+        <v>10951</v>
       </c>
       <c r="AL7" s="4">
         <f t="shared" si="2"/>
-        <v>6331</v>
+        <v>5436</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.35">
@@ -1235,9 +1258,11 @@
         <v>602</v>
       </c>
       <c r="R8" s="1">
-        <v>3669</v>
-      </c>
-      <c r="S8" s="1"/>
+        <v>6549</v>
+      </c>
+      <c r="S8" s="1">
+        <v>330</v>
+      </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1257,11 +1282,11 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2">
         <f t="shared" si="1"/>
-        <v>13123</v>
+        <v>16333</v>
       </c>
       <c r="AL8" s="4">
         <f t="shared" si="2"/>
-        <v>2631</v>
+        <v>-579</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.35">
@@ -1311,7 +1336,9 @@
       <c r="R9" s="1">
         <v>4366</v>
       </c>
-      <c r="S9" s="1"/>
+      <c r="S9" s="1">
+        <v>332</v>
+      </c>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -1331,11 +1358,11 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2">
         <f t="shared" si="1"/>
-        <v>9381</v>
+        <v>9713</v>
       </c>
       <c r="AL9" s="4">
         <f t="shared" si="2"/>
-        <v>24634</v>
+        <v>24302</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1401,11 +1428,11 @@
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>22131</v>
+        <v>26531</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1965</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="3"/>
@@ -1477,11 +1504,11 @@
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="1"/>
-        <v>62017</v>
+        <v>68382</v>
       </c>
       <c r="AL10" s="6">
         <f t="shared" ref="AL10:AL11" si="4">D10-AK10</f>
-        <v>22544</v>
+        <v>16179</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1547,11 +1574,11 @@
       </c>
       <c r="R11" s="5">
         <f t="shared" si="5"/>
-        <v>553.27499999999998</v>
+        <v>663.27499999999998</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>49.125</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="5"/>
@@ -1623,11 +1650,11 @@
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="1"/>
-        <v>1550.4250000000002</v>
+        <v>1709.5500000000002</v>
       </c>
       <c r="AL11" s="6">
         <f t="shared" si="4"/>
-        <v>563.59999999999991</v>
+        <v>404.47499999999991</v>
       </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.35">
@@ -2063,28 +2090,60 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+      <c r="A43" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="1">
+        <v>60</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
+      <c r="A44" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="A45" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="1">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="A46" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="1">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
@@ -2267,7 +2326,7 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>1185.825</v>
+        <v>1268.825</v>
       </c>
       <c r="D76" s="1"/>
     </row>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7774586D-D048-48BF-A528-2466C8055DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2173C4E8-B2A6-4504-841D-B72F8CE41928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -187,13 +187,37 @@
   </si>
   <si>
     <t xml:space="preserve">Jalal Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arshad Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Season </t>
+  </si>
+  <si>
+    <t>Crown Market Singh pura</t>
+  </si>
+  <si>
+    <t>Jalal sons  Main Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raja Saab Wapda Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mb/SB Traders  Shadbagh </t>
+  </si>
+  <si>
+    <t>Sweera GT Road</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +236,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -286,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -300,9 +332,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -327,13 +356,19 @@
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,71 +683,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AL76"/>
+  <dimension ref="A1:AM76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="9.453125" customWidth="1"/>
-    <col min="15" max="15" width="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="9.453125" customWidth="1"/>
-    <col min="20" max="35" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.7265625" customWidth="1"/>
+    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="9.453125" customWidth="1"/>
+    <col min="16" max="16" width="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="9.453125" customWidth="1"/>
+    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.453125" customWidth="1"/>
+    <col min="23" max="23" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.453125" customWidth="1"/>
+    <col min="26" max="36" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="6.08984375" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9">
+    <row r="1" spans="1:39" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8">
         <v>46260</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-    </row>
-    <row r="2" spans="1:38" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+    </row>
+    <row r="2" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -722,110 +762,113 @@
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>46243</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14">
+        <v>46253</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="10">
+      <c r="H2" s="9">
         <v>1</v>
       </c>
-      <c r="H2" s="10">
+      <c r="I2" s="9">
         <v>2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="J2" s="9">
         <v>3</v>
       </c>
-      <c r="J2" s="10">
+      <c r="K2" s="9">
         <v>4</v>
       </c>
-      <c r="K2" s="10">
+      <c r="L2" s="9">
         <v>5</v>
       </c>
-      <c r="L2" s="10">
+      <c r="M2" s="9">
         <v>6</v>
       </c>
-      <c r="M2" s="10">
+      <c r="N2" s="9">
         <v>7</v>
       </c>
-      <c r="N2" s="10">
+      <c r="O2" s="9">
         <v>8</v>
       </c>
-      <c r="O2" s="10">
+      <c r="P2" s="9">
         <v>9</v>
       </c>
-      <c r="P2" s="10">
+      <c r="Q2" s="9">
         <v>10</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="R2" s="9">
         <v>11</v>
       </c>
-      <c r="R2" s="10">
+      <c r="S2" s="9">
         <v>12</v>
       </c>
-      <c r="S2" s="10">
+      <c r="T2" s="9">
         <v>13</v>
       </c>
-      <c r="T2" s="10">
+      <c r="U2" s="9">
         <v>14</v>
       </c>
-      <c r="U2" s="10">
+      <c r="V2" s="9">
         <v>15</v>
       </c>
-      <c r="V2" s="10">
+      <c r="W2" s="9">
         <v>16</v>
       </c>
-      <c r="W2" s="10">
+      <c r="X2" s="9">
         <v>17</v>
       </c>
-      <c r="X2" s="10">
+      <c r="Y2" s="9">
         <v>18</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="Z2" s="9">
         <v>19</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="AA2" s="9">
         <v>20</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AB2" s="9">
         <v>21</v>
       </c>
-      <c r="AB2" s="10">
-        <v>22</v>
-      </c>
-      <c r="AC2" s="10">
+      <c r="AC2" s="9">
+        <v>22</v>
+      </c>
+      <c r="AD2" s="9">
         <v>23</v>
       </c>
-      <c r="AD2" s="10">
+      <c r="AE2" s="9">
         <v>24</v>
       </c>
-      <c r="AE2" s="10">
+      <c r="AF2" s="9">
         <v>25</v>
       </c>
-      <c r="AF2" s="10">
+      <c r="AG2" s="9">
         <v>26</v>
       </c>
-      <c r="AG2" s="10">
+      <c r="AH2" s="9">
         <v>27</v>
       </c>
-      <c r="AH2" s="10">
+      <c r="AI2" s="9">
         <v>28</v>
       </c>
-      <c r="AI2" s="10">
+      <c r="AJ2" s="9">
         <v>29</v>
       </c>
-      <c r="AJ2" s="10">
+      <c r="AK2" s="9">
         <v>30</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AL2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AM2" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,50 +882,58 @@
         <v>8000</v>
       </c>
       <c r="F3" s="1">
-        <f>E3+D3</f>
-        <v>14769</v>
+        <v>4000</v>
       </c>
       <c r="G3" s="1">
+        <f>D3+E3+F3</f>
+        <v>18769</v>
+      </c>
+      <c r="H3" s="1">
         <v>75</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="1">
+      <c r="I3" s="6"/>
+      <c r="J3" s="1">
         <v>144</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>92</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>260</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>770</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>279</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>939</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="1">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="1">
         <v>642</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>300</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>2268</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <v>184</v>
       </c>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="1">
+        <v>250</v>
+      </c>
+      <c r="W3" s="6"/>
+      <c r="X3" s="1">
+        <v>250</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>390</v>
+      </c>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -894,16 +945,17 @@
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
-      <c r="AK3" s="2">
-        <f>SUM(G3:AJ3)</f>
-        <v>5953</v>
-      </c>
-      <c r="AL3" s="4">
-        <f>F3-AK3</f>
-        <v>8816</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="2">
+        <f>SUM(H3:AK3)</f>
+        <v>6843</v>
+      </c>
+      <c r="AM3" s="4">
+        <f t="shared" ref="AM3:AM9" si="0">G3-AL3</f>
+        <v>11926</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -917,50 +969,58 @@
         <v>8000</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:F9" si="0">E4+D4</f>
-        <v>11137</v>
+        <v>4000</v>
       </c>
       <c r="G4" s="1">
+        <f t="shared" ref="G4:G9" si="1">D4+E4+F4</f>
+        <v>15137</v>
+      </c>
+      <c r="H4" s="1">
         <v>40</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="1">
+      <c r="I4" s="6"/>
+      <c r="J4" s="1">
         <v>113</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>92</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>240</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>582</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>481</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>1041</v>
       </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="1">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="1">
         <v>812</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>337</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>2028</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <v>158</v>
       </c>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="1">
+        <v>363</v>
+      </c>
+      <c r="W4" s="6"/>
+      <c r="X4" s="1">
+        <v>258</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>421</v>
+      </c>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
@@ -972,16 +1032,17 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="2">
-        <f t="shared" ref="AK4:AK11" si="1">SUM(G4:AJ4)</f>
-        <v>5924</v>
-      </c>
-      <c r="AL4" s="4">
-        <f t="shared" ref="AL4:AL9" si="2">F4-AK4</f>
-        <v>5213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="2">
+        <f t="shared" ref="AL4:AL9" si="2">SUM(H4:AK4)</f>
+        <v>6966</v>
+      </c>
+      <c r="AM4" s="4">
+        <f t="shared" si="0"/>
+        <v>8171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -995,50 +1056,58 @@
         <v>8000</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="0"/>
-        <v>15361</v>
+        <v>4000</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>19361</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6"/>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
         <v>240</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>679</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>179</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>3557</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="1">
+      <c r="P5" s="6"/>
+      <c r="Q5" s="1">
         <v>770</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>215</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>1290</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <v>339</v>
       </c>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="1">
+        <v>305</v>
+      </c>
+      <c r="W5" s="6"/>
+      <c r="X5" s="1">
+        <v>116</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>742</v>
+      </c>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -1050,16 +1119,17 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="2">
-        <f t="shared" si="1"/>
-        <v>7269</v>
-      </c>
-      <c r="AL5" s="4">
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="2">
         <f t="shared" si="2"/>
-        <v>8092</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+        <v>8432</v>
+      </c>
+      <c r="AM5" s="4">
+        <f t="shared" si="0"/>
+        <v>10929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,50 +1141,58 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>13138</v>
+        <v>12000</v>
       </c>
       <c r="G6" s="1">
+        <f t="shared" si="1"/>
+        <v>25138</v>
+      </c>
+      <c r="H6" s="1">
         <v>228</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="1">
+      <c r="I6" s="6"/>
+      <c r="J6" s="1">
         <v>190</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>240</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>667</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>1577</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>539</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>1264</v>
       </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="1">
+      <c r="P6" s="6"/>
+      <c r="Q6" s="1">
         <v>947</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>574</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>5646</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <v>367</v>
       </c>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="1">
+        <v>389</v>
+      </c>
+      <c r="W6" s="6"/>
+      <c r="X6" s="1">
+        <v>365</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>649</v>
+      </c>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
@@ -1126,16 +1204,17 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="2">
-        <f t="shared" si="1"/>
-        <v>12239</v>
-      </c>
-      <c r="AL6" s="4">
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="2">
         <f t="shared" si="2"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+        <v>13642</v>
+      </c>
+      <c r="AM6" s="4">
+        <f t="shared" si="0"/>
+        <v>11496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1149,50 +1228,58 @@
         <v>12000</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>16387</v>
+        <v>4000</v>
       </c>
       <c r="G7" s="1">
+        <f t="shared" si="1"/>
+        <v>20387</v>
+      </c>
+      <c r="H7" s="1">
         <v>257</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="1">
+      <c r="I7" s="6"/>
+      <c r="J7" s="1">
         <v>175</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>170</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>730</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>1572</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>398</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>1562</v>
       </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="1">
+      <c r="P7" s="6"/>
+      <c r="Q7" s="1">
         <v>1059</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>389</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>4384</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <v>255</v>
       </c>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="1">
+        <v>602</v>
+      </c>
+      <c r="W7" s="6"/>
+      <c r="X7" s="1">
+        <v>330</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>794</v>
+      </c>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -1204,16 +1291,17 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
-      <c r="AK7" s="2">
-        <f t="shared" si="1"/>
-        <v>10951</v>
-      </c>
-      <c r="AL7" s="4">
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="2">
         <f t="shared" si="2"/>
-        <v>5436</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+        <v>12677</v>
+      </c>
+      <c r="AM7" s="4">
+        <f t="shared" si="0"/>
+        <v>7710</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1225,50 +1313,58 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
-        <f t="shared" si="0"/>
-        <v>15754</v>
+        <v>12000</v>
       </c>
       <c r="G8" s="1">
+        <f t="shared" si="1"/>
+        <v>27754</v>
+      </c>
+      <c r="H8" s="1">
         <v>187</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="1">
+      <c r="I8" s="6"/>
+      <c r="J8" s="1">
         <v>235</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>220</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>753</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>2315</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>946</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>2794</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="1">
+      <c r="P8" s="6"/>
+      <c r="Q8" s="1">
         <v>1402</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>602</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>6549</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <v>330</v>
       </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="1">
+        <v>648</v>
+      </c>
+      <c r="W8" s="6"/>
+      <c r="X8" s="1">
+        <v>370</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>834</v>
+      </c>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
@@ -1280,16 +1376,17 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
-      <c r="AK8" s="2">
-        <f t="shared" si="1"/>
-        <v>16333</v>
-      </c>
-      <c r="AL8" s="4">
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="2">
         <f t="shared" si="2"/>
-        <v>-579</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+        <v>18185</v>
+      </c>
+      <c r="AM8" s="4">
+        <f t="shared" si="0"/>
+        <v>9569</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,51 +1397,57 @@
         <v>34015</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1">
-        <f t="shared" si="0"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <f t="shared" si="1"/>
         <v>34015</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>252</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="1">
+      <c r="I9" s="6"/>
+      <c r="J9" s="1">
         <v>255</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>292</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>447</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>2234</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>263</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>148</v>
       </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="1">
+      <c r="P9" s="6"/>
+      <c r="Q9" s="1">
         <v>652</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>472</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>4366</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <v>332</v>
       </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="1">
+        <v>484</v>
+      </c>
+      <c r="W9" s="6"/>
+      <c r="X9" s="1">
+        <v>364</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>391</v>
+      </c>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
@@ -1356,16 +1459,17 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="2">
-        <f t="shared" si="1"/>
-        <v>9713</v>
-      </c>
-      <c r="AL9" s="4">
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="2">
         <f t="shared" si="2"/>
-        <v>24302</v>
-      </c>
-    </row>
-    <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>10952</v>
+      </c>
+      <c r="AM9" s="4">
+        <f t="shared" si="0"/>
+        <v>23063</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1380,71 +1484,71 @@
       </c>
       <c r="F10" s="5">
         <f>SUM(F3:F9)</f>
-        <v>120561</v>
+        <v>40000</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" ref="G10:AJ10" si="3">SUM(G3:G9)</f>
+        <f>SUM(G3:G9)</f>
+        <v>160561</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" ref="H10:AM10" si="3">SUM(H3:H9)</f>
         <v>1039</v>
       </c>
-      <c r="H10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="I10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="3"/>
         <v>1112</v>
       </c>
-      <c r="J10" s="5">
+      <c r="K10" s="5">
         <f t="shared" si="3"/>
         <v>1106</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="5">
         <f t="shared" si="3"/>
         <v>3337</v>
       </c>
-      <c r="L10" s="5">
+      <c r="M10" s="5">
         <f t="shared" si="3"/>
         <v>9729</v>
       </c>
-      <c r="M10" s="5">
+      <c r="N10" s="5">
         <f t="shared" si="3"/>
         <v>3085</v>
       </c>
-      <c r="N10" s="5">
+      <c r="O10" s="5">
         <f t="shared" si="3"/>
         <v>11305</v>
       </c>
-      <c r="O10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="3"/>
         <v>6284</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="R10" s="5">
         <f t="shared" si="3"/>
         <v>2889</v>
       </c>
-      <c r="R10" s="5">
+      <c r="S10" s="5">
         <f t="shared" si="3"/>
         <v>26531</v>
       </c>
-      <c r="S10" s="5">
+      <c r="T10" s="5">
         <f t="shared" si="3"/>
         <v>1965</v>
       </c>
-      <c r="T10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3041</v>
       </c>
       <c r="W10" s="5">
         <f t="shared" si="3"/>
@@ -1452,11 +1556,11 @@
       </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2053</v>
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4221</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="3"/>
@@ -1503,15 +1607,19 @@
         <v>0</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="1"/>
-        <v>68382</v>
-      </c>
-      <c r="AL10" s="6">
-        <f t="shared" ref="AL10:AL11" si="4">D10-AK10</f>
-        <v>16179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:38" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="5">
+        <f t="shared" si="3"/>
+        <v>77697</v>
+      </c>
+      <c r="AM10" s="5">
+        <f t="shared" si="3"/>
+        <v>82864</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1526,148 +1634,153 @@
       </c>
       <c r="F11" s="5">
         <f>F10/40</f>
-        <v>3014.0250000000001</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" ref="G11:AJ11" si="5">G10/40</f>
+        <v>1000</v>
+      </c>
+      <c r="G11" s="16">
+        <f>G10/40</f>
+        <v>4014.0250000000001</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" ref="H11:AM11" si="4">H10/40</f>
         <v>25.975000000000001</v>
       </c>
-      <c r="H11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="I11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="4"/>
         <v>27.8</v>
       </c>
-      <c r="J11" s="5">
-        <f t="shared" si="5"/>
+      <c r="K11" s="5">
+        <f t="shared" si="4"/>
         <v>27.65</v>
       </c>
-      <c r="K11" s="5">
-        <f t="shared" si="5"/>
+      <c r="L11" s="5">
+        <f t="shared" si="4"/>
         <v>83.424999999999997</v>
       </c>
-      <c r="L11" s="5">
-        <f t="shared" si="5"/>
+      <c r="M11" s="5">
+        <f t="shared" si="4"/>
         <v>243.22499999999999</v>
       </c>
-      <c r="M11" s="5">
-        <f t="shared" si="5"/>
+      <c r="N11" s="5">
+        <f t="shared" si="4"/>
         <v>77.125</v>
       </c>
-      <c r="N11" s="5">
-        <f t="shared" si="5"/>
+      <c r="O11" s="5">
+        <f t="shared" si="4"/>
         <v>282.625</v>
       </c>
-      <c r="O11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="P11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="4"/>
         <v>157.1</v>
       </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="5"/>
+      <c r="R11" s="5">
+        <f t="shared" si="4"/>
         <v>72.224999999999994</v>
       </c>
-      <c r="R11" s="5">
-        <f t="shared" si="5"/>
+      <c r="S11" s="5">
+        <f t="shared" si="4"/>
         <v>663.27499999999998</v>
       </c>
-      <c r="S11" s="5">
-        <f t="shared" si="5"/>
+      <c r="T11" s="5">
+        <f t="shared" si="4"/>
         <v>49.125</v>
       </c>
-      <c r="T11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="U11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>76.025000000000006</v>
       </c>
       <c r="W11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>51.325000000000003</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>105.52500000000001</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AB11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="1"/>
-        <v>1709.5500000000002</v>
-      </c>
-      <c r="AL11" s="6">
-        <f t="shared" si="4"/>
-        <v>404.47499999999991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="16">
+        <f t="shared" si="4"/>
+        <v>1942.425</v>
+      </c>
+      <c r="AM11" s="17">
+        <f t="shared" si="4"/>
+        <v>2071.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1680,11 +1793,12 @@
       <c r="D13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A14" s="8">
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
         <v>46239</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1697,8 +1811,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A15" s="8">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
         <v>46239</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1711,8 +1825,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
         <v>46240</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1726,7 +1840,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>46240</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1740,7 +1854,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>46240</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1754,7 +1868,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>46240</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1768,7 +1882,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <v>46240</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1782,7 +1896,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>46240</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1796,7 +1910,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <v>46241</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1810,7 +1924,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <v>46241</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1824,7 +1938,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
+      <c r="A24" s="7">
         <v>46242</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1838,7 +1952,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <v>46242</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1852,7 +1966,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
+      <c r="A26" s="7">
         <v>46242</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1866,7 +1980,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
+      <c r="A27" s="7">
         <v>46242</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1880,7 +1994,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
+      <c r="A28" s="7">
         <v>46242</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1894,7 +2008,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <v>46242</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1908,7 +2022,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8">
+      <c r="A30" s="7">
         <v>46244</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1922,7 +2036,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="8">
+      <c r="A31" s="7">
         <v>46244</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1936,7 +2050,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
+      <c r="A32" s="7">
         <v>46244</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1950,7 +2064,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
+      <c r="A33" s="7">
         <v>46244</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1964,7 +2078,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
+      <c r="A34" s="7">
         <v>46244</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1978,7 +2092,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
+      <c r="A35" s="7">
         <v>46245</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -1992,7 +2106,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="8">
+      <c r="A36" s="7">
         <v>46245</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2006,7 +2120,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="8">
+      <c r="A37" s="7">
         <v>46246</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2020,7 +2134,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="8">
+      <c r="A38" s="7">
         <v>46246</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2034,7 +2148,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="8">
+      <c r="A39" s="7">
         <v>46246</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2048,7 +2162,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="8">
+      <c r="A40" s="7">
         <v>46246</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2062,7 +2176,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="8">
+      <c r="A41" s="7">
         <v>46246</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2076,7 +2190,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="8">
+      <c r="A42" s="7">
         <v>46246</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2090,10 +2204,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="8">
+      <c r="A43" s="7">
         <v>46246</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C43" s="1">
@@ -2104,7 +2218,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="8">
+      <c r="A44" s="7">
         <v>46247</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -2118,7 +2232,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="8">
+      <c r="A45" s="7">
         <v>46247</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2132,7 +2246,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="8">
+      <c r="A46" s="7">
         <v>46247</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2146,58 +2260,130 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="A47" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="1">
+        <v>5</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="A48" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="1">
+        <v>12.975</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="A49" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="1">
+        <v>23</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+      <c r="A50" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="1">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+      <c r="A51" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="1">
+        <v>4.9749999999999996</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+      <c r="A52" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="A53" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="1">
+        <v>15</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="A54" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="1">
+        <v>12</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+      <c r="A55" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="1">
+        <v>30</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -2326,15 +2512,16 @@
       <c r="B76" s="1"/>
       <c r="C76" s="4">
         <f>SUM(C14:C75)</f>
-        <v>1268.825</v>
+        <v>1387.9749999999999</v>
       </c>
       <c r="D76" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:AL1"/>
+    <mergeCell ref="B1:AM1"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2173C4E8-B2A6-4504-841D-B72F8CE41928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1B3572-CC8E-4506-B6DA-0DBF3A60851E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -683,31 +683,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AM76"/>
+  <dimension ref="A1:AN76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.7265625" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="9.453125" customWidth="1"/>
-    <col min="16" max="16" width="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="9.453125" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.453125" customWidth="1"/>
-    <col min="23" max="23" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="9.453125" customWidth="1"/>
-    <col min="26" max="36" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="8.7265625" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.453125" customWidth="1"/>
+    <col min="17" max="17" width="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="9.453125" customWidth="1"/>
+    <col min="22" max="22" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" customWidth="1"/>
+    <col min="24" max="24" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="37" width="9.453125" customWidth="1"/>
+    <col min="38" max="38" width="6.08984375" customWidth="1"/>
+    <col min="39" max="39" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:40" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8">
         <v>46260</v>
       </c>
@@ -751,8 +750,9 @@
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
-    </row>
-    <row r="2" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AN1" s="18"/>
+    </row>
+    <row r="2" spans="1:40" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -768,107 +768,110 @@
       <c r="F2" s="14">
         <v>46253</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="14">
+        <v>46257</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>1</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <v>2</v>
       </c>
-      <c r="J2" s="9">
+      <c r="K2" s="9">
         <v>3</v>
       </c>
-      <c r="K2" s="9">
+      <c r="L2" s="9">
         <v>4</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <v>5</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <v>6</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <v>7</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <v>8</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <v>9</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>10</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>11</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="9">
         <v>12</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <v>13</v>
       </c>
-      <c r="U2" s="9">
+      <c r="V2" s="9">
         <v>14</v>
       </c>
-      <c r="V2" s="9">
+      <c r="W2" s="9">
         <v>15</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="9">
         <v>16</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <v>17</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Z2" s="9">
         <v>18</v>
       </c>
-      <c r="Z2" s="9">
+      <c r="AA2" s="9">
         <v>19</v>
       </c>
-      <c r="AA2" s="9">
+      <c r="AB2" s="9">
         <v>20</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AC2" s="9">
         <v>21</v>
       </c>
-      <c r="AC2" s="9">
-        <v>22</v>
-      </c>
       <c r="AD2" s="9">
+        <v>22</v>
+      </c>
+      <c r="AE2" s="9">
         <v>23</v>
       </c>
-      <c r="AE2" s="9">
+      <c r="AF2" s="9">
         <v>24</v>
       </c>
-      <c r="AF2" s="9">
+      <c r="AG2" s="9">
         <v>25</v>
       </c>
-      <c r="AG2" s="9">
+      <c r="AH2" s="9">
         <v>26</v>
       </c>
-      <c r="AH2" s="9">
+      <c r="AI2" s="9">
         <v>27</v>
       </c>
-      <c r="AI2" s="9">
+      <c r="AJ2" s="9">
         <v>28</v>
       </c>
-      <c r="AJ2" s="9">
+      <c r="AK2" s="9">
         <v>29</v>
       </c>
-      <c r="AK2" s="9">
+      <c r="AL2" s="9">
         <v>30</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AM2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AM2" s="11" t="s">
+      <c r="AN2" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -885,56 +888,58 @@
         <v>4000</v>
       </c>
       <c r="G3" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H3" s="1">
         <f>D3+E3+F3</f>
         <v>18769</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>75</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="1">
+      <c r="J3" s="6"/>
+      <c r="K3" s="1">
         <v>144</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>92</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>260</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>770</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>279</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" s="1">
         <v>939</v>
       </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="1">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="1">
         <v>642</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>300</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <v>2268</v>
       </c>
-      <c r="T3" s="1">
+      <c r="U3" s="1">
         <v>184</v>
       </c>
-      <c r="U3" s="6"/>
-      <c r="V3" s="1">
+      <c r="V3" s="6"/>
+      <c r="W3" s="1">
         <v>250</v>
       </c>
-      <c r="W3" s="6"/>
-      <c r="X3" s="1">
+      <c r="X3" s="6"/>
+      <c r="Y3" s="1">
         <v>250</v>
       </c>
-      <c r="Y3" s="1">
+      <c r="Z3" s="1">
         <v>390</v>
       </c>
-      <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
@@ -946,16 +951,17 @@
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
-      <c r="AL3" s="2">
-        <f>SUM(H3:AK3)</f>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="2">
+        <f>SUM(I3:AL3)</f>
         <v>6843</v>
       </c>
-      <c r="AM3" s="4">
-        <f t="shared" ref="AM3:AM9" si="0">G3-AL3</f>
+      <c r="AN3" s="4">
+        <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
         <v>11926</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,56 +978,58 @@
         <v>4000</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" ref="G4:G9" si="1">D4+E4+F4</f>
+        <v>4000</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" ref="H4:H9" si="1">D4+E4+F4</f>
         <v>15137</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>40</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="1">
+      <c r="J4" s="6"/>
+      <c r="K4" s="1">
         <v>113</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>92</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>240</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>582</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>481</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>1041</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="1">
+      <c r="Q4" s="6"/>
+      <c r="R4" s="1">
         <v>812</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>337</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <v>2028</v>
       </c>
-      <c r="T4" s="1">
+      <c r="U4" s="1">
         <v>158</v>
       </c>
-      <c r="U4" s="6"/>
-      <c r="V4" s="1">
+      <c r="V4" s="6"/>
+      <c r="W4" s="1">
         <v>363</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="1">
+      <c r="X4" s="6"/>
+      <c r="Y4" s="1">
         <v>258</v>
       </c>
-      <c r="Y4" s="1">
+      <c r="Z4" s="1">
         <v>421</v>
       </c>
-      <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
@@ -1033,16 +1041,17 @@
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
-      <c r="AL4" s="2">
-        <f t="shared" ref="AL4:AL9" si="2">SUM(H4:AK4)</f>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="2">
+        <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
         <v>6966</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AN4" s="4">
         <f t="shared" si="0"/>
         <v>8171</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,56 +1068,58 @@
         <v>4000</v>
       </c>
       <c r="G5" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H5" s="1">
         <f t="shared" si="1"/>
         <v>19361</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6"/>
       <c r="K5" s="1">
         <v>0</v>
       </c>
       <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
         <v>240</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>679</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>179</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>3557</v>
       </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="1">
+      <c r="Q5" s="6"/>
+      <c r="R5" s="1">
         <v>770</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>215</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <v>1290</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>339</v>
       </c>
-      <c r="U5" s="6"/>
-      <c r="V5" s="1">
+      <c r="V5" s="6"/>
+      <c r="W5" s="1">
         <v>305</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="1">
+      <c r="X5" s="6"/>
+      <c r="Y5" s="1">
         <v>116</v>
       </c>
-      <c r="Y5" s="1">
+      <c r="Z5" s="1">
         <v>742</v>
       </c>
-      <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -1120,16 +1131,17 @@
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
-      <c r="AL5" s="2">
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="2">
         <f t="shared" si="2"/>
         <v>8432</v>
       </c>
-      <c r="AM5" s="4">
+      <c r="AN5" s="4">
         <f t="shared" si="0"/>
         <v>10929</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
@@ -1144,56 +1156,58 @@
         <v>12000</v>
       </c>
       <c r="G6" s="1">
+        <v>8000</v>
+      </c>
+      <c r="H6" s="1">
         <f t="shared" si="1"/>
         <v>25138</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>228</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="1">
+      <c r="J6" s="6"/>
+      <c r="K6" s="1">
         <v>190</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>240</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>667</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>1577</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>539</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>1264</v>
       </c>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="1">
+      <c r="Q6" s="6"/>
+      <c r="R6" s="1">
         <v>947</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>574</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <v>5646</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>367</v>
       </c>
-      <c r="U6" s="6"/>
-      <c r="V6" s="1">
+      <c r="V6" s="6"/>
+      <c r="W6" s="1">
         <v>389</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="1">
+      <c r="X6" s="6"/>
+      <c r="Y6" s="1">
         <v>365</v>
       </c>
-      <c r="Y6" s="1">
+      <c r="Z6" s="1">
         <v>649</v>
       </c>
-      <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -1205,16 +1219,17 @@
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
-      <c r="AL6" s="2">
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="2">
         <f t="shared" si="2"/>
         <v>13642</v>
       </c>
-      <c r="AM6" s="4">
+      <c r="AN6" s="4">
         <f t="shared" si="0"/>
         <v>11496</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1231,56 +1246,58 @@
         <v>4000</v>
       </c>
       <c r="G7" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H7" s="1">
         <f t="shared" si="1"/>
         <v>20387</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>257</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="1">
+      <c r="J7" s="6"/>
+      <c r="K7" s="1">
         <v>175</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>170</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>730</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>1572</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>398</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>1562</v>
       </c>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="1">
+      <c r="Q7" s="6"/>
+      <c r="R7" s="1">
         <v>1059</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>389</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <v>4384</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>255</v>
       </c>
-      <c r="U7" s="6"/>
-      <c r="V7" s="1">
+      <c r="V7" s="6"/>
+      <c r="W7" s="1">
         <v>602</v>
       </c>
-      <c r="W7" s="6"/>
-      <c r="X7" s="1">
+      <c r="X7" s="6"/>
+      <c r="Y7" s="1">
         <v>330</v>
       </c>
-      <c r="Y7" s="1">
+      <c r="Z7" s="1">
         <v>794</v>
       </c>
-      <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -1292,16 +1309,17 @@
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
-      <c r="AL7" s="2">
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="2">
         <f t="shared" si="2"/>
         <v>12677</v>
       </c>
-      <c r="AM7" s="4">
+      <c r="AN7" s="4">
         <f t="shared" si="0"/>
         <v>7710</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1316,56 +1334,58 @@
         <v>12000</v>
       </c>
       <c r="G8" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H8" s="1">
         <f t="shared" si="1"/>
         <v>27754</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>187</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="1">
+      <c r="J8" s="6"/>
+      <c r="K8" s="1">
         <v>235</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>220</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>753</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>2315</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>946</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>2794</v>
       </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="1">
+      <c r="Q8" s="6"/>
+      <c r="R8" s="1">
         <v>1402</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>602</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <v>6549</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>330</v>
       </c>
-      <c r="U8" s="6"/>
-      <c r="V8" s="1">
+      <c r="V8" s="6"/>
+      <c r="W8" s="1">
         <v>648</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="1">
+      <c r="X8" s="6"/>
+      <c r="Y8" s="1">
         <v>370</v>
       </c>
-      <c r="Y8" s="1">
+      <c r="Z8" s="1">
         <v>834</v>
       </c>
-      <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -1377,16 +1397,17 @@
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
-      <c r="AL8" s="2">
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="2">
         <f t="shared" si="2"/>
         <v>18185</v>
       </c>
-      <c r="AM8" s="4">
+      <c r="AN8" s="4">
         <f t="shared" si="0"/>
         <v>9569</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1398,57 +1419,57 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <f t="shared" si="1"/>
         <v>34015</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>252</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="1">
+      <c r="J9" s="6"/>
+      <c r="K9" s="1">
         <v>255</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>292</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>447</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>2234</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>263</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>148</v>
       </c>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="1">
+      <c r="Q9" s="6"/>
+      <c r="R9" s="1">
         <v>652</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>472</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <v>4366</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <v>332</v>
       </c>
-      <c r="U9" s="6"/>
-      <c r="V9" s="1">
+      <c r="V9" s="6"/>
+      <c r="W9" s="1">
         <v>484</v>
       </c>
-      <c r="W9" s="6"/>
-      <c r="X9" s="1">
+      <c r="X9" s="6"/>
+      <c r="Y9" s="1">
         <v>364</v>
       </c>
-      <c r="Y9" s="1">
+      <c r="Z9" s="1">
         <v>391</v>
       </c>
-      <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -1460,16 +1481,17 @@
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
-      <c r="AL9" s="2">
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="2">
         <f t="shared" si="2"/>
         <v>10952</v>
       </c>
-      <c r="AM9" s="4">
+      <c r="AN9" s="4">
         <f t="shared" si="0"/>
         <v>23063</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1488,84 +1510,84 @@
       </c>
       <c r="G10" s="5">
         <f>SUM(G3:G9)</f>
+        <v>40000</v>
+      </c>
+      <c r="H10" s="5">
+        <f>SUM(H3:H9)</f>
         <v>160561</v>
       </c>
-      <c r="H10" s="5">
-        <f t="shared" ref="H10:AM10" si="3">SUM(H3:H9)</f>
+      <c r="I10" s="5">
+        <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
         <v>1039</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="J10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="3"/>
         <v>1112</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="5">
         <f t="shared" si="3"/>
         <v>1106</v>
       </c>
-      <c r="L10" s="5">
+      <c r="M10" s="5">
         <f t="shared" si="3"/>
         <v>3337</v>
       </c>
-      <c r="M10" s="5">
+      <c r="N10" s="5">
         <f t="shared" si="3"/>
         <v>9729</v>
       </c>
-      <c r="N10" s="5">
+      <c r="O10" s="5">
         <f t="shared" si="3"/>
         <v>3085</v>
       </c>
-      <c r="O10" s="5">
+      <c r="P10" s="5">
         <f t="shared" si="3"/>
         <v>11305</v>
       </c>
-      <c r="P10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="3"/>
         <v>6284</v>
       </c>
-      <c r="R10" s="5">
+      <c r="S10" s="5">
         <f t="shared" si="3"/>
         <v>2889</v>
       </c>
-      <c r="S10" s="5">
+      <c r="T10" s="5">
         <f t="shared" si="3"/>
         <v>26531</v>
       </c>
-      <c r="T10" s="5">
+      <c r="U10" s="5">
         <f t="shared" si="3"/>
         <v>1965</v>
       </c>
-      <c r="U10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="V10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <f t="shared" si="3"/>
         <v>3041</v>
       </c>
-      <c r="W10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
+        <f t="shared" si="3"/>
         <v>2053</v>
       </c>
-      <c r="Y10" s="5">
+      <c r="Z10" s="5">
         <f t="shared" si="3"/>
         <v>4221</v>
       </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="AA10" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -1612,14 +1634,18 @@
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="5">
+        <f t="shared" si="3"/>
         <v>77697</v>
       </c>
-      <c r="AM10" s="5">
+      <c r="AN10" s="5">
         <f t="shared" si="3"/>
         <v>82864</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1636,86 +1662,86 @@
         <f>F10/40</f>
         <v>1000</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="5">
         <f>G10/40</f>
+        <v>1000</v>
+      </c>
+      <c r="H11" s="16">
+        <f>H10/40</f>
         <v>4014.0250000000001</v>
       </c>
-      <c r="H11" s="5">
-        <f t="shared" ref="H11:AM11" si="4">H10/40</f>
+      <c r="I11" s="5">
+        <f t="shared" ref="I11:AN11" si="4">I10/40</f>
         <v>25.975000000000001</v>
       </c>
-      <c r="I11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="J11" s="5">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="4"/>
         <v>27.8</v>
       </c>
-      <c r="K11" s="5">
+      <c r="L11" s="5">
         <f t="shared" si="4"/>
         <v>27.65</v>
       </c>
-      <c r="L11" s="5">
+      <c r="M11" s="5">
         <f t="shared" si="4"/>
         <v>83.424999999999997</v>
       </c>
-      <c r="M11" s="5">
+      <c r="N11" s="5">
         <f t="shared" si="4"/>
         <v>243.22499999999999</v>
       </c>
-      <c r="N11" s="5">
+      <c r="O11" s="5">
         <f t="shared" si="4"/>
         <v>77.125</v>
       </c>
-      <c r="O11" s="5">
+      <c r="P11" s="5">
         <f t="shared" si="4"/>
         <v>282.625</v>
       </c>
-      <c r="P11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="Q11" s="5">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="4"/>
         <v>157.1</v>
       </c>
-      <c r="R11" s="5">
+      <c r="S11" s="5">
         <f t="shared" si="4"/>
         <v>72.224999999999994</v>
       </c>
-      <c r="S11" s="5">
+      <c r="T11" s="5">
         <f t="shared" si="4"/>
         <v>663.27499999999998</v>
       </c>
-      <c r="T11" s="5">
+      <c r="U11" s="5">
         <f t="shared" si="4"/>
         <v>49.125</v>
       </c>
-      <c r="U11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="V11" s="5">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" si="4"/>
         <v>76.025000000000006</v>
       </c>
-      <c r="W11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="X11" s="5">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <f t="shared" si="4"/>
         <v>51.325000000000003</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="Z11" s="5">
         <f t="shared" si="4"/>
         <v>105.52500000000001</v>
       </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="AA11" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1760,16 +1786,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="16">
+      <c r="AL11" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="16">
         <f t="shared" si="4"/>
         <v>1942.425</v>
       </c>
-      <c r="AM11" s="17">
+      <c r="AN11" s="17">
         <f t="shared" si="4"/>
         <v>2071.6</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>16</v>
       </c>
@@ -1779,8 +1809,9 @@
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1796,8 +1827,9 @@
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>46239</v>
       </c>
@@ -1811,7 +1843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>46239</v>
       </c>
@@ -1825,7 +1857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>46240</v>
       </c>
@@ -2518,7 +2550,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:AM1"/>
+    <mergeCell ref="B1:AN1"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Aug_2026/daily Reports/Monthly.xlsx
+++ b/Aug_2026/daily Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF40D010-EB8E-4EA9-9A23-512518377C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9BF9BD-16A7-4E44-AD5D-20C1C584DC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -318,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -369,7 +369,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2006,9 +2005,6 @@
       <c r="D15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
@@ -2023,11 +2019,8 @@
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>46240</v>
       </c>
@@ -2040,11 +2033,8 @@
       <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>46240</v>
       </c>
@@ -2057,11 +2047,8 @@
       <c r="D18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>46240</v>
       </c>
@@ -2074,11 +2061,8 @@
       <c r="D19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>46240</v>
       </c>
@@ -2091,11 +2075,8 @@
       <c r="D20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>46240</v>
       </c>
@@ -2108,11 +2089,8 @@
       <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>46241</v>
       </c>
@@ -2125,11 +2103,8 @@
       <c r="D22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>46241</v>
       </c>
@@ -2143,7 +2118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>46242</v>
       </c>
@@ -2157,7 +2132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>46242</v>
       </c>
@@ -2171,7 +2146,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>46242</v>
       </c>
@@ -2185,7 +2160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>46242</v>
       </c>
@@ -2199,7 +2174,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>46242</v>
       </c>
@@ -2213,7 +2188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>46242</v>
       </c>
@@ -2227,7 +2202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>46244</v>
       </c>
@@ -2241,7 +2216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>46244</v>
       </c>
@@ -2255,7 +2230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>46244</v>
       </c>
